--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABD0479B-BBA5-4EFF-9DFE-F8E01C02B865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D08C6A-3C9E-43E5-AB0D-6ACAD953B689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1110" yWindow="3470" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8360" yWindow="10300" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,10 +67,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FunctionGrpup</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>功能组</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -146,11 +142,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>对话|送礼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10+10+10+10+11</t>
+  </si>
+  <si>
+    <t>PointerDialogue</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点击对话</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FunctionGroup</t>
+  </si>
+  <si>
+    <t>对话|送礼|布料店</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -197,7 +204,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -207,6 +214,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF258"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4E83FD"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -249,7 +268,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -270,6 +289,12 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -552,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.6640625" style="1"/>
@@ -560,13 +585,13 @@
     <col min="5" max="5" width="23.75" customWidth="1"/>
     <col min="6" max="6" width="17.58203125" customWidth="1"/>
     <col min="7" max="7" width="21.08203125" customWidth="1"/>
-    <col min="8" max="8" width="23.25" customWidth="1"/>
-    <col min="9" max="9" width="21.4140625" customWidth="1"/>
-    <col min="10" max="10" width="16.58203125" customWidth="1"/>
-    <col min="11" max="11" width="27.25" customWidth="1"/>
+    <col min="8" max="9" width="23.25" customWidth="1"/>
+    <col min="10" max="10" width="21.4140625" customWidth="1"/>
+    <col min="11" max="11" width="16.58203125" customWidth="1"/>
+    <col min="12" max="12" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -577,31 +602,34 @@
         <v>6</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>27</v>
+      <c r="K1" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="L1" s="7" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -615,10 +643,10 @@
         <v>4</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>7</v>
@@ -627,16 +655,19 @@
         <v>7</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
+      </c>
+      <c r="L2" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -647,72 +678,81 @@
         <v>8</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>10000</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" s="3">
         <v>10000</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="I4" s="1">
-        <v>10001</v>
-      </c>
-      <c r="J4" s="1"/>
-      <c r="K4" s="3"/>
+        <v>25</v>
+      </c>
+      <c r="I4" s="8">
+        <v>10000</v>
+      </c>
+      <c r="J4" s="9">
+        <v>10100</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" s="1">
         <v>10003</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="I5" s="1">
-        <v>10001</v>
-      </c>
-      <c r="K5" s="1">
+        <v>30</v>
+      </c>
+      <c r="I5" s="8">
+        <v>10000</v>
+      </c>
+      <c r="J5" s="9">
+        <v>10101</v>
+      </c>
+      <c r="L5" s="1">
         <v>100001</v>
       </c>
     </row>

--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92D08C6A-3C9E-43E5-AB0D-6ACAD953B689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCE3386-90F5-433F-99AF-B727CE857D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8360" yWindow="10300" windowWidth="38610" windowHeight="16040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-6450" yWindow="6060" windowWidth="38610" windowHeight="15710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>##var</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,14 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FunctionType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>功能组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FavorMax</t>
   </si>
   <si>
@@ -88,20 +80,6 @@
     <t>FavorUnlock</t>
   </si>
   <si>
-    <t>DailyDialogue</t>
-  </si>
-  <si>
-    <t>日常对话</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PlotDialogue</t>
-  </si>
-  <si>
-    <t>剧情对话</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>(list#sep=+),long</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -114,57 +92,22 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NpcID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>资源配置表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10+10+10+10+10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>ShowRule</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>场景列表</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>商店小妹</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>无</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10+10+10+10+11</t>
-  </si>
-  <si>
-    <t>PointerDialogue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>点击对话</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FunctionGroup</t>
-  </si>
-  <si>
-    <t>对话|送礼|布料店</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -174,14 +117,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
@@ -204,33 +139,15 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF258"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4E83FD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -253,49 +170,20 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFDEE0E3"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFDEE0E3"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -577,21 +465,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="8.6640625" style="1"/>
-    <col min="4" max="4" width="35.58203125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.75" customWidth="1"/>
-    <col min="6" max="6" width="17.58203125" customWidth="1"/>
-    <col min="7" max="7" width="21.08203125" customWidth="1"/>
-    <col min="8" max="9" width="23.25" customWidth="1"/>
-    <col min="10" max="10" width="21.4140625" customWidth="1"/>
-    <col min="11" max="11" width="16.58203125" customWidth="1"/>
-    <col min="12" max="12" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="17.58203125" customWidth="1"/>
+    <col min="5" max="5" width="21.08203125" customWidth="1"/>
+    <col min="6" max="6" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -601,35 +484,17 @@
       <c r="C1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="L1" s="7" t="s">
-        <v>26</v>
-      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -639,35 +504,17 @@
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="D2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -677,83 +524,36 @@
       <c r="C3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>24</v>
+      <c r="D3" s="1" t="s">
+        <v>10</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="J3" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>10000</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="B4" s="3">
-        <v>10000</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="3">
-        <v>10000</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="I4" s="8">
-        <v>10000</v>
-      </c>
-      <c r="J4" s="9">
-        <v>10100</v>
-      </c>
-      <c r="K4" s="1"/>
-      <c r="L4" s="3"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B5" s="1">
         <v>10001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="1">
-        <v>10003</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I5" s="8">
-        <v>10000</v>
-      </c>
-      <c r="J5" s="9">
-        <v>10101</v>
-      </c>
-      <c r="L5" s="1">
-        <v>100001</v>
+        <v>18</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -1,24 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFCE3386-90F5-433F-99AF-B727CE857D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6450" yWindow="6060" windowWidth="38610" windowHeight="15710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="真实角色" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -28,76 +30,60 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>##var</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Remark</t>
+  </si>
+  <si>
+    <t>FavorMax</t>
+  </si>
+  <si>
+    <t>FavorStageReward</t>
+  </si>
+  <si>
+    <t>FavorUnlock</t>
   </si>
   <si>
     <t>##type</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>(list#sep=+),long</t>
   </si>
   <si>
     <t>##</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>唯一ID</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Remark</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>备注</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FavorMax</t>
   </si>
   <si>
     <t>好感度上限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FavorStageReward</t>
   </si>
   <si>
     <t>好感度阶段奖励</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>FavorUnlock</t>
-  </si>
-  <si>
-    <t>(list#sep=+),long</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>好感解锁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>男主</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10+10+10+10+10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>商店小妹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>10+10+10+10+11</t>
@@ -106,19 +92,18 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -126,7 +111,6 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -134,20 +118,356 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -170,33 +490,319 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -245,7 +851,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Calibri Light"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
@@ -280,7 +886,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
@@ -454,87 +1060,82 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="3" width="8.6640625" style="1"/>
-    <col min="4" max="4" width="17.58203125" customWidth="1"/>
-    <col min="5" max="5" width="21.08203125" customWidth="1"/>
+    <col min="1" max="3" width="8.66666666666667" style="1"/>
+    <col min="4" max="4" width="17.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="21.0833333333333" customWidth="1"/>
     <col min="6" max="6" width="23.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6">
       <c r="B4" s="2">
         <v>10000</v>
       </c>
@@ -545,7 +1146,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6">
       <c r="B5" s="1">
         <v>10001</v>
       </c>
@@ -557,8 +1158,8 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
   <si>
     <t>##var</t>
   </si>
@@ -80,13 +80,40 @@
     <t>男主</t>
   </si>
   <si>
-    <t>10+10+10+10+10</t>
-  </si>
-  <si>
-    <t>商店小妹</t>
-  </si>
-  <si>
-    <t>10+10+10+10+11</t>
+    <t>马吉</t>
+  </si>
+  <si>
+    <t>100+120+150+180+200</t>
+  </si>
+  <si>
+    <t>紅院 栗花</t>
+  </si>
+  <si>
+    <t>紗夜</t>
+  </si>
+  <si>
+    <t>紫苑</t>
+  </si>
+  <si>
+    <t>友莉</t>
+  </si>
+  <si>
+    <t>桃</t>
+  </si>
+  <si>
+    <t>千织</t>
+  </si>
+  <si>
+    <t>紬</t>
+  </si>
+  <si>
+    <t>巧蜜</t>
+  </si>
+  <si>
+    <t>一郎</t>
+  </si>
+  <si>
+    <t>二爺</t>
   </si>
 </sst>
 </file>
@@ -99,7 +126,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,25 +135,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="等线"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -591,161 +609,170 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1066,95 +1093,204 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="4" outlineLevelCol="5"/>
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="3" width="8.66666666666667" style="1"/>
-    <col min="4" max="4" width="17.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="21.0833333333333" customWidth="1"/>
-    <col min="6" max="6" width="23.25" customWidth="1"/>
+    <col min="4" max="4" width="24.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="21.0833333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.25" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="B4" s="2">
+      <c r="B4" s="4">
         <v>10000</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5" s="4">
+        <v>10001</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="B5" s="1">
-        <v>10001</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="1" t="s">
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6" s="4">
+        <v>10002</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>19</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7" s="1">
+        <v>10003</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8" s="4">
+        <v>10004</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="B9" s="4">
+        <v>10005</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="B10" s="4">
+        <v>10006</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="B11" s="1">
+        <v>10007</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="B12" s="4">
+        <v>10008</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="B13" s="4">
+        <v>10009</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="B14" s="4">
+        <v>10010</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="B15" s="1">
+        <v>10011</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D15" s="2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>##var</t>
   </si>
@@ -114,6 +114,15 @@
   </si>
   <si>
     <t>二爺</t>
+  </si>
+  <si>
+    <t>赌场(娃娃机)</t>
+  </si>
+  <si>
+    <t>赌场(毒药)</t>
+  </si>
+  <si>
+    <t>赌场(爆点)</t>
   </si>
 </sst>
 </file>
@@ -754,14 +763,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1093,104 +1096,104 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="3" width="8.66666666666667" style="1"/>
-    <col min="4" max="4" width="24.75" style="2" customWidth="1"/>
-    <col min="5" max="5" width="21.0833333333333" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.25" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="2" width="8.66666666666667" style="1"/>
+    <col min="3" max="3" width="12.1666666666667" style="1" customWidth="1"/>
+    <col min="4" max="4" width="24.75" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.0833333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="23.25" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="B4" s="4">
+      <c r="B4" s="2">
         <v>10000</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="B5" s="4">
+      <c r="B5" s="2">
         <v>10001</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="B6" s="4">
+      <c r="B6" s="2">
         <v>10002</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1198,43 +1201,43 @@
       <c r="B7" s="1">
         <v>10003</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="B8" s="4">
+      <c r="B8" s="2">
         <v>10004</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="B9" s="4">
+      <c r="B9" s="2">
         <v>10005</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="B10" s="4">
+      <c r="B10" s="2">
         <v>10006</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="2">
+      <c r="D10" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1242,43 +1245,43 @@
       <c r="B11" s="1">
         <v>10007</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="2">
+      <c r="D11" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="B12" s="4">
+      <c r="B12" s="2">
         <v>10008</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="2">
+      <c r="D12" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="B13" s="4">
+      <c r="B13" s="2">
         <v>10009</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D13" s="2">
+      <c r="D13" s="1">
         <v>100</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="B14" s="4">
+      <c r="B14" s="2">
         <v>10010</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="D14" s="2">
+      <c r="D14" s="1">
         <v>100</v>
       </c>
     </row>
@@ -1286,11 +1289,35 @@
       <c r="B15" s="1">
         <v>10011</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="1">
         <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="B16" s="1">
+        <v>10012</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
+      <c r="B17" s="1">
+        <v>10013</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
+      <c r="B18" s="1">
+        <v>10014</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A4C6CD-B406-41EF-810A-25ABD699FE5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="2530" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17230"/>
   </bookViews>
   <sheets>
     <sheet name="真实角色" sheetId="1" r:id="rId1"/>
@@ -53,6 +47,9 @@
     <t>FavorUnlock</t>
   </si>
   <si>
+    <t>ClothingList</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
     <t>好感解锁</t>
   </si>
   <si>
+    <t>服装列表</t>
+  </si>
+  <si>
     <t>男主</t>
   </si>
   <si>
@@ -92,6 +92,9 @@
     <t>100+120+150+180+200</t>
   </si>
   <si>
+    <t>10001+10002+10003+10004+10005+10006+10007+10008+10009</t>
+  </si>
+  <si>
     <t>紅院 栗花</t>
   </si>
   <si>
@@ -129,25 +132,19 @@
   </si>
   <si>
     <t>赌场(爆点)</t>
-  </si>
-  <si>
-    <t>ClothingList</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>服装列表</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>10001+10002+10003+10004+10005</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,33 +156,354 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -208,9 +526,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -224,17 +784,61 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -492,25 +1096,25 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:G18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="1"/>
-    <col min="3" max="3" width="12.1640625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.66666666666667" style="1"/>
+    <col min="3" max="3" width="12.1666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.75" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.08203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.0833333333333" style="1" customWidth="1"/>
     <col min="6" max="6" width="23.25" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.1666666666667" style="1" customWidth="1"/>
     <col min="8" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -530,214 +1134,214 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="F2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
       <c r="B4" s="2">
         <v>10000</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5" s="2">
         <v>10001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6" s="2">
         <v>10002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7" s="1">
         <v>10003</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8" s="2">
         <v>10004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9" s="2">
         <v>10005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D9" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7">
       <c r="B10" s="2">
         <v>10006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="D10" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7">
       <c r="B11" s="1">
         <v>10007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D11" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7">
       <c r="B12" s="2">
         <v>10008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D12" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7">
       <c r="B13" s="2">
         <v>10009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7">
       <c r="B14" s="2">
         <v>10010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7">
       <c r="B15" s="1">
         <v>10011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D15" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7">
       <c r="B16" s="1">
         <v>10012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3">
       <c r="B17" s="1">
         <v>10013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3">
       <c r="B18" s="1">
         <v>10014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95249091-2800-4561-9871-64F661640BC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10300" yWindow="1290" windowWidth="30590" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="真实角色" sheetId="1" r:id="rId1"/>
@@ -33,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
   <si>
     <t>##var</t>
   </si>
@@ -44,6 +38,9 @@
     <t>Remark</t>
   </si>
   <si>
+    <t>Name</t>
+  </si>
+  <si>
     <t>FavorMax</t>
   </si>
   <si>
@@ -65,6 +62,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>TbLocalzationKeyData#sep=+</t>
+  </si>
+  <si>
     <t>(list#sep=+),long</t>
   </si>
   <si>
@@ -77,6 +77,9 @@
     <t>备注</t>
   </si>
   <si>
+    <t>名字</t>
+  </si>
+  <si>
     <t>好感度上限</t>
   </si>
   <si>
@@ -92,10 +95,16 @@
     <t>男主</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_01</t>
+  </si>
+  <si>
     <t>马吉</t>
   </si>
   <si>
-    <t>100+120+150+180+200</t>
+    <t>CharacterNames+Character_NPC_02</t>
+  </si>
+  <si>
+    <t>100+100+100+100+100+100+100+100+100+100</t>
   </si>
   <si>
     <t>10001+10002+10003+10004+10005+10006+10007+10008+10009</t>
@@ -104,94 +113,79 @@
     <t>紅院 栗花</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_03</t>
+  </si>
+  <si>
+    <t>100+100+100+100+100</t>
+  </si>
+  <si>
     <t>紗夜</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_04</t>
+  </si>
+  <si>
     <t>紫苑</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_05</t>
+  </si>
+  <si>
     <t>友莉</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_06</t>
+  </si>
+  <si>
     <t>桃</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_07</t>
+  </si>
+  <si>
     <t>千织</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_08</t>
+  </si>
+  <si>
     <t>紬</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_09</t>
+  </si>
+  <si>
     <t>巧蜜</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_10</t>
+  </si>
+  <si>
     <t>一郎</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_11</t>
+  </si>
+  <si>
     <t>二爺</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_12</t>
+  </si>
+  <si>
     <t>赌场(娃娃机)</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_13</t>
+  </si>
+  <si>
     <t>赌场(毒药)</t>
   </si>
   <si>
+    <t>CharacterNames+Character_NPC_14</t>
+  </si>
+  <si>
     <t>赌场(爆点)</t>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>名字</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_02</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_03</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_04</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_05</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_06</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_07</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_08</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_09</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_10</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_11</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_12</t>
-  </si>
-  <si>
-    <t>TbLocalzationKeyData#sep=+</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_13</t>
-  </si>
-  <si>
-    <t>CharacterNames+Character_NPC_14</t>
   </si>
   <si>
     <t>CharacterNames+Character_NPC_15</t>
@@ -200,8 +194,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,31 +213,354 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -260,36 +583,322 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -547,26 +1156,26 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="1"/>
-    <col min="3" max="3" width="12.1640625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.66666666666667" style="1"/>
+    <col min="3" max="3" width="12.1666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="43.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="24.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.08203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="50.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.0833333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="35.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="35.1666666666667" style="1" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,278 +1185,278 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
       <c r="H1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="F2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="H2" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>36</v>
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="B4" s="3">
         <v>10000</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="3">
         <v>10001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B6" s="2">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="3">
         <v>10002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="B7" s="1">
         <v>10003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B8" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="B8" s="3">
         <v>10004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B9" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="3">
         <v>10005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E9" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B10" s="2">
+    <row r="10" spans="1:8">
+      <c r="B10" s="3">
         <v>10006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E10" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8">
       <c r="B11" s="1">
         <v>10007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E11" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B12" s="2">
+    <row r="12" spans="1:8">
+      <c r="B12" s="3">
         <v>10008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="E12" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B13" s="2">
+    <row r="13" spans="1:8">
+      <c r="B13" s="3">
         <v>10009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E13" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="B14" s="2">
+    <row r="14" spans="1:8">
+      <c r="B14" s="3">
         <v>10010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E14" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8">
       <c r="B15" s="1">
         <v>10011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E15" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8">
       <c r="B16" s="1">
         <v>10012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
       <c r="B17" s="1">
         <v>10013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:4">
       <c r="B18" s="1">
         <v>10014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4B636D-1860-4D3E-8D31-2C86B9C65FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView xWindow="0" yWindow="2500" windowWidth="39220" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="真实角色" sheetId="1" r:id="rId1"/>
@@ -27,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -189,19 +195,21 @@
   </si>
   <si>
     <t>CharacterNames+Character_NPC_15</t>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>DefaultClothing</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="22">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,354 +221,31 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <charset val="134"/>
+      <family val="2"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <sz val="9"/>
       <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -583,253 +268,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -843,62 +286,24 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1156,26 +561,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="8.66666666666667" style="1"/>
-    <col min="3" max="3" width="12.1666666666667" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.6640625" style="1"/>
+    <col min="3" max="3" width="12.1640625" style="1" customWidth="1"/>
     <col min="4" max="4" width="43.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50.3333333333333" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.0833333333333" style="1" customWidth="1"/>
+    <col min="5" max="5" width="50.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.08203125" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="35.1666666666667" style="1" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="1"/>
+    <col min="8" max="8" width="47.75" style="5" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1197,11 +603,14 @@
       <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,11 +632,14 @@
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -1249,11 +661,11 @@
       <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B4" s="3">
         <v>10000</v>
       </c>
@@ -1264,7 +676,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9" ht="33" x14ac:dyDescent="0.3">
       <c r="B5" s="3">
         <v>10001</v>
       </c>
@@ -1277,11 +689,14 @@
       <c r="E5" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="5" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1">
+        <v>10001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B6" s="3">
         <v>10002</v>
       </c>
@@ -1295,7 +710,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B7" s="1">
         <v>10003</v>
       </c>
@@ -1309,7 +724,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B8" s="3">
         <v>10004</v>
       </c>
@@ -1323,7 +738,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B9" s="3">
         <v>10005</v>
       </c>
@@ -1337,7 +752,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B10" s="3">
         <v>10006</v>
       </c>
@@ -1351,7 +766,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B11" s="1">
         <v>10007</v>
       </c>
@@ -1365,7 +780,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B12" s="3">
         <v>10008</v>
       </c>
@@ -1379,7 +794,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B13" s="3">
         <v>10009</v>
       </c>
@@ -1393,7 +808,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B14" s="3">
         <v>10010</v>
       </c>
@@ -1407,7 +822,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B15" s="1">
         <v>10011</v>
       </c>
@@ -1421,7 +836,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B16" s="1">
         <v>10012</v>
       </c>
@@ -1432,7 +847,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="17" spans="2:4">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B17" s="1">
         <v>10013</v>
       </c>
@@ -1443,7 +858,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="2:4">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
       <c r="B18" s="1">
         <v>10014</v>
       </c>
@@ -1455,8 +870,8 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA4B636D-1860-4D3E-8D31-2C86B9C65FE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5710F33E-2253-4374-9683-459DD5428F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2500" windowWidth="39220" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1420" windowWidth="39220" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="真实角色" sheetId="1" r:id="rId1"/>
@@ -110,9 +110,6 @@
     <t>CharacterNames+Character_NPC_02</t>
   </si>
   <si>
-    <t>100+100+100+100+100+100+100+100+100+100</t>
-  </si>
-  <si>
     <t>10001+10002+10003+10004+10005+10006+10007+10008+10009</t>
   </si>
   <si>
@@ -202,6 +199,10 @@
   </si>
   <si>
     <t>DefaultClothing</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>100+200+300+400+500</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -607,7 +608,7 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
@@ -636,7 +637,7 @@
         <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
@@ -687,10 +688,10 @@
         <v>24</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>25</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>26</v>
       </c>
       <c r="I5" s="1">
         <v>10001</v>
@@ -701,13 +702,13 @@
         <v>10002</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
@@ -715,13 +716,13 @@
         <v>10003</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="E7" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
@@ -729,13 +730,13 @@
         <v>10004</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="E8" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
@@ -743,10 +744,10 @@
         <v>10005</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="E9" s="1">
         <v>100</v>
@@ -757,10 +758,10 @@
         <v>10006</v>
       </c>
       <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="E10" s="1">
         <v>100</v>
@@ -771,10 +772,10 @@
         <v>10007</v>
       </c>
       <c r="C11" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>39</v>
       </c>
       <c r="E11" s="1">
         <v>100</v>
@@ -785,10 +786,10 @@
         <v>10008</v>
       </c>
       <c r="C12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>40</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>41</v>
       </c>
       <c r="E12" s="1">
         <v>100</v>
@@ -799,10 +800,10 @@
         <v>10009</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="E13" s="1">
         <v>100</v>
@@ -813,10 +814,10 @@
         <v>10010</v>
       </c>
       <c r="C14" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>44</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>45</v>
       </c>
       <c r="E14" s="1">
         <v>100</v>
@@ -827,10 +828,10 @@
         <v>10011</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>47</v>
       </c>
       <c r="E15" s="1">
         <v>100</v>
@@ -841,10 +842,10 @@
         <v>10012</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.3">
@@ -852,10 +853,10 @@
         <v>10013</v>
       </c>
       <c r="C17" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.3">
@@ -863,10 +864,10 @@
         <v>10014</v>
       </c>
       <c r="C18" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
   </sheetData>

--- a/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
+++ b/ExcelTool/LubanTools/DataTables/Datas/CharacterData.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitLabProject\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\AFramework\ExcelTool\LubanTools\DataTables\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5710F33E-2253-4374-9683-459DD5428F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1420" windowWidth="39220" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="真实角色" sheetId="1" r:id="rId1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="55">
   <si>
     <t>##var</t>
   </si>
@@ -59,6 +58,9 @@
     <t>ClothingList</t>
   </si>
   <si>
+    <t>DefaultClothing</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -110,6 +112,9 @@
     <t>CharacterNames+Character_NPC_02</t>
   </si>
   <si>
+    <t>100+200+300+400+500</t>
+  </si>
+  <si>
     <t>10001+10002+10003+10004+10005+10006+10007+10008+10009</t>
   </si>
   <si>
@@ -192,25 +197,19 @@
   </si>
   <si>
     <t>CharacterNames+Character_NPC_15</t>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>DefaultClothing</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>100+200+300+400+500</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,31 +221,354 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -269,9 +591,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -279,6 +843,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -287,24 +854,65 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -562,27 +1170,27 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="2" width="8.6640625" style="1"/>
-    <col min="3" max="3" width="12.1640625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="8.66666666666667" style="1"/>
+    <col min="3" max="3" width="12.1666666666667" style="1" customWidth="1"/>
     <col min="4" max="4" width="43.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="50.33203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="21.08203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="50.3333333333333" style="1" customWidth="1"/>
+    <col min="6" max="6" width="21.0833333333333" style="1" customWidth="1"/>
     <col min="7" max="7" width="23.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="47.75" style="5" customWidth="1"/>
-    <col min="9" max="9" width="16.33203125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="47.75" style="2" customWidth="1"/>
+    <col min="9" max="9" width="16.3333333333333" style="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -592,287 +1200,287 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
       <c r="E3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="5" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="3">
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="B4" s="4">
         <v>10000</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="33" x14ac:dyDescent="0.3">
-      <c r="B5" s="3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" ht="33" spans="1:9">
+      <c r="B5" s="4">
         <v>10001</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="I5" s="1">
         <v>10001</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="3">
+    <row r="6" spans="1:9">
+      <c r="B6" s="4">
         <v>10002</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="B7" s="1">
         <v>10003</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="3">
+    </row>
+    <row r="8" spans="1:9">
+      <c r="B8" s="4">
         <v>10004</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="B9" s="4">
         <v>10005</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E9" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="3">
+    <row r="10" spans="1:9">
+      <c r="B10" s="4">
         <v>10006</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E10" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9">
       <c r="B11" s="1">
         <v>10007</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E11" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="3">
+    <row r="12" spans="1:9">
+      <c r="B12" s="4">
         <v>10008</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E12" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="3">
+    <row r="13" spans="1:9">
+      <c r="B13" s="4">
         <v>10009</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E13" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="3">
+    <row r="14" spans="1:9">
+      <c r="B14" s="4">
         <v>10010</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E14" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9">
       <c r="B15" s="1">
         <v>10011</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E15" s="1">
         <v>100</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9">
       <c r="B16" s="1">
         <v>10012</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4">
       <c r="B17" s="1">
         <v>10013</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4">
       <c r="B18" s="1">
         <v>10014</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>